--- a/artfynd/A 24410-2026 artfynd.xlsx
+++ b/artfynd/A 24410-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89736797</v>
+        <v>89736798</v>
       </c>
       <c r="B2" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534168.2201217777</v>
+        <v>534168</v>
       </c>
       <c r="R2" t="n">
-        <v>6324902.883978619</v>
+        <v>6324903</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -801,15 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89736798</v>
+        <v>89736797</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +807,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -855,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534168.2201217777</v>
+        <v>534168</v>
       </c>
       <c r="R3" t="n">
-        <v>6324902.883978619</v>
+        <v>6324903</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
